--- a/data/human/adult/validation/Scenarios/NervousValidation.xlsx
+++ b/data/human/adult/validation/Scenarios/NervousValidation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\documentation\source\data\human\adult\validation\Scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\release_updates\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0F4C61-AB52-4C54-A672-AA3CA27CC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6A32B7-F100-40AC-B934-1A50F3E9AA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6330" yWindow="9615" windowWidth="22365" windowHeight="17955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="23445" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -71,21 +71,12 @@
     <t>|</t>
   </si>
   <si>
-    <t>Increase ~30% @cite Hosomi1979effect @cite Ottesen2004applied</t>
-  </si>
-  <si>
     <t>&lt;/span&gt;|</t>
   </si>
   <si>
     <t>&lt;/span&gt;|&lt;span class="warning"&gt;</t>
   </si>
   <si>
-    <t>Decrease ~15-20% @cite Hosomi1979effect @cite Ottesen2004applied</t>
-  </si>
-  <si>
-    <t>Increase 10-15% @cite Hosomi1979effect @cite Ottesen2004applied</t>
-  </si>
-  <si>
     <t>---</t>
   </si>
   <si>
@@ -204,6 +195,15 @@
   </si>
   <si>
     <t>Brain Injury (TBI)</t>
+  </si>
+  <si>
+    <t>Decrease ~15-20% @cite hosomi1979effect @cite ottesen2004applied</t>
+  </si>
+  <si>
+    <t>Increase ~30% @cite hosomi1979effect @cite ottesen2004applied</t>
+  </si>
+  <si>
+    <t>Increase 10-15% @cite hosomi1979effect @cite ottesen2004applied</t>
   </si>
 </sst>
 </file>
@@ -743,7 +743,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -811,15 +811,6 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="44" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -831,9 +822,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="48">
@@ -1207,179 +1195,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="28" t="s">
+      <c r="C1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="23" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="26" t="s">
+      <c r="A2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26" t="s">
-        <v>19</v>
+      <c r="E3" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F3" s="8">
         <v>3</v>
       </c>
-      <c r="G3" s="26" t="s">
-        <v>12</v>
+      <c r="G3" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="H3" s="9">
         <v>0</v>
       </c>
-      <c r="I3" s="26" t="s">
-        <v>23</v>
+      <c r="I3" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="J3" s="11">
         <v>0</v>
       </c>
-      <c r="K3" s="26" t="s">
-        <v>11</v>
+      <c r="K3" s="23" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="A4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>19</v>
+        <v>44</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F4" s="8">
         <v>23</v>
       </c>
-      <c r="G4" s="26" t="s">
-        <v>12</v>
+      <c r="G4" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="H4" s="9">
         <v>2</v>
       </c>
-      <c r="I4" s="26" t="s">
-        <v>23</v>
+      <c r="I4" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="J4" s="11">
         <v>0</v>
       </c>
-      <c r="K4" s="26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="K4" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="19"/>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="23" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="22">
         <f>SUM(F3,F4)</f>
         <v>26</v>
       </c>
-      <c r="G5" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="23">
+      <c r="G5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="9">
         <f>SUM(H3,H4)</f>
         <v>2</v>
       </c>
-      <c r="I5" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="24">
+      <c r="I5" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="11">
         <f>SUM(J3,J4)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="30" t="s">
-        <v>11</v>
+      <c r="K5" s="23" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1475,19 +1463,19 @@
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
@@ -1504,37 +1492,37 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>9</v>
@@ -1560,25 +1548,25 @@
         <v>200</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H4" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1611,7 @@
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1662,43 +1650,43 @@
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>9</v>
@@ -1709,55 +1697,55 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>9</v>
@@ -1768,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>9</v>
@@ -1789,37 +1777,37 @@
         <v>600</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>42</v>
-      </c>
       <c r="Q4" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="75" x14ac:dyDescent="0.25">
@@ -1827,13 +1815,13 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>9</v>
@@ -1848,37 +1836,37 @@
         <v>900</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" x14ac:dyDescent="0.25">
@@ -1886,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>9</v>
@@ -1907,37 +1895,37 @@
         <v>1700</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="O6" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="75" x14ac:dyDescent="0.25">
@@ -1945,13 +1933,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>9</v>
@@ -1966,37 +1954,37 @@
         <v>2000</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
@@ -2004,13 +1992,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
@@ -2025,37 +2013,37 @@
         <v>3220</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="O8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2064,18 +2052,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2193,14 +2181,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF1B20E2-65A5-4DC5-B5E1-EAEF16402220}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6320210A-C44C-4B82-8349-5A58CB3B5A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -2211,6 +2191,14 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF1B20E2-65A5-4DC5-B5E1-EAEF16402220}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
